--- a/psychopy_exp_files/sequences/learning_block4_fixed-middle-10_59.xlsx
+++ b/psychopy_exp_files/sequences/learning_block4_fixed-middle-10_59.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_16.jpg</t>
+          <t>stimuli/jacket/jacket_14.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>15</v>
       </c>
       <c r="V2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W2" t="n">
         <v>16</v>
@@ -668,17 +668,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_14.jpg</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_16.jpg</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_14.jpg</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_06.jpg</t>
+          <t>stimuli/house/house_34.jpg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -688,17 +688,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -734,13 +734,13 @@
         <v>15</v>
       </c>
       <c r="U3" t="n">
+        <v>10</v>
+      </c>
+      <c r="V3" t="n">
         <v>5</v>
       </c>
-      <c r="V3" t="n">
-        <v>10</v>
-      </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -762,7 +762,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_16.jpg</t>
+          <t>stimuli/jacket/jacket_14.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -830,13 +830,13 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U4" t="n">
         <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W4" t="n">
         <v>14</v>
@@ -866,12 +866,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_49.jpg</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_28.jpg</t>
+          <t>stimuli/hammer/hammer_43.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -932,10 +932,10 @@
         <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W5" t="n">
         <v>16</v>
@@ -960,42 +960,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_28.jpg</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_06.jpg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_49.jpg</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_43.jpg</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_18.jpg</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_06.jpg</t>
+          <t>stimuli/house/house_34.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1028,16 +1028,16 @@
         <v>6</v>
       </c>
       <c r="T6" t="n">
+        <v>6</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
+      </c>
+      <c r="V6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>7</v>
-      </c>
-      <c r="V6" t="n">
-        <v>8</v>
-      </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -1059,19 +1059,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_06.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_18.jpg</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_22.jpg</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_34.jpg</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>stimuli/pencil/pencil_11.jpg</t>
@@ -1079,17 +1079,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1127,13 +1127,13 @@
         <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
+        <v>8</v>
+      </c>
+      <c r="V7" t="n">
         <v>4</v>
-      </c>
-      <c r="V7" t="n">
-        <v>9</v>
       </c>
       <c r="W7" t="n">
         <v>16</v>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/ball/ball_49.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1178,12 +1178,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1226,10 +1226,10 @@
         <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
         <v>16</v>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/ball/ball_49.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_28.jpg</t>
+          <t>stimuli/hammer/hammer_43.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1272,17 +1272,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_06.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1325,16 +1325,16 @@
         <v>9</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V9" t="n">
         <v>15</v>
       </c>
       <c r="W9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1356,42 +1356,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_43.jpg</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_16.jpg</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_40.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_14.jpg</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>stimuli/lamp/lamp_40.jpg</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_49.jpg</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>ball</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1424,16 +1424,16 @@
         <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V10" t="n">
         <v>14</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1455,12 +1455,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_14.jpg</t>
+          <t>stimuli/dog/dog_16.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/house/house_34.jpg</t>
+          <t>stimuli/chair/chair_22.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1470,17 +1470,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/ball/ball_49.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1523,16 +1523,16 @@
         <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
         <v>18</v>
       </c>
       <c r="W11" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1554,42 +1554,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_22.jpg</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>stimuli/house/house_34.jpg</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_18.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>stimuli/bicycle/bicycle_06.jpg</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_18.jpg</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_43.jpg</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hammer</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1622,16 +1622,16 @@
         <v>12</v>
       </c>
       <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
         <v>9</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2</v>
       </c>
       <c r="V12" t="n">
         <v>3</v>
       </c>
       <c r="W12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_06.jpg</t>
+          <t>stimuli/house/house_34.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_28.jpg</t>
+          <t>stimuli/hammer/hammer_43.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1721,7 +1721,7 @@
         <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U13" t="n">
         <v>14</v>
@@ -1730,7 +1730,7 @@
         <v>15</v>
       </c>
       <c r="W13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_16.jpg</t>
+          <t>stimuli/jacket/jacket_14.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1826,10 +1826,10 @@
         <v>16</v>
       </c>
       <c r="V14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_23.jpg</t>
+          <t>stimuli/house/house_41.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1925,7 +1925,7 @@
         <v>16</v>
       </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W15" t="n">
         <v>17</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/house/house_41.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2021,7 +2021,7 @@
         <v>16</v>
       </c>
       <c r="U16" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="V16" t="n">
         <v>3</v>
@@ -2049,17 +2049,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>stimuli/house/house_41.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/hand/hand_23.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_15.jpg</t>
+          <t>stimuli/hammer/hammer_21.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2069,17 +2069,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2117,13 +2117,13 @@
         <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="U17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W17" t="n">
         <v>17</v>
@@ -2148,17 +2148,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/hand/hand_23.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_44.jpg</t>
+          <t>stimuli/flower/flower_15.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/jacket/jacket_20.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2168,17 +2168,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2216,13 +2216,13 @@
         <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W18" t="n">
         <v>15</v>
@@ -2247,12 +2247,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_44.jpg</t>
+          <t>stimuli/flower/flower_15.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/jacket/jacket_20.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2262,17 +2262,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>stimuli/house/house_41.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2315,16 +2315,16 @@
         <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V19" t="n">
         <v>15</v>
       </c>
       <c r="W19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/jacket/jacket_20.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_15.jpg</t>
+          <t>stimuli/hammer/hammer_21.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2361,17 +2361,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/hand/hand_23.jpg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2414,16 +2414,16 @@
         <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V20" t="n">
         <v>16</v>
       </c>
       <c r="W20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -2445,17 +2445,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_15.jpg</t>
+          <t>stimuli/hammer/hammer_21.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_23.jpg</t>
+          <t>stimuli/house/house_41.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_23.jpg</t>
+          <t>stimuli/ball/ball_44.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2465,17 +2465,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2513,13 +2513,13 @@
         <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W21" t="n">
         <v>3</v>
@@ -2544,17 +2544,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_23.jpg</t>
+          <t>stimuli/house/house_41.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_23.jpg</t>
+          <t>stimuli/ball/ball_44.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_20.jpg</t>
+          <t>stimuli/dog/dog_10.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2564,17 +2564,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2612,13 +2612,13 @@
         <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U22" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="V22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
         <v>17</v>
@@ -2643,42 +2643,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_23.jpg</t>
+          <t>stimuli/ball/ball_44.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_23.jpg</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_15.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_21.jpg</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_44.jpg</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_15.jpg</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>hammer</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2711,16 +2711,16 @@
         <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6</v>
+      </c>
+      <c r="W23" t="n">
         <v>7</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1</v>
-      </c>
-      <c r="W23" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_21.jpg</t>
+          <t>stimuli/bicycle/bicycle_23.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_20.jpg</t>
+          <t>stimuli/dog/dog_10.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2810,13 +2810,13 @@
         <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>3</v>
       </c>
       <c r="V24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
         <v>17</v>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_20.jpg</t>
+          <t>stimuli/dog/dog_10.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/hand/hand_23.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2912,13 +2912,13 @@
         <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V25" t="n">
         <v>15</v>
       </c>
       <c r="W25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_20.jpg</t>
+          <t>stimuli/dog/dog_10.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_21.jpg</t>
+          <t>stimuli/bicycle/bicycle_23.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3008,7 +3008,7 @@
         <v>13</v>
       </c>
       <c r="T26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U26" t="n">
         <v>13</v>
@@ -3017,7 +3017,7 @@
         <v>16</v>
       </c>
       <c r="W26" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_44.jpg</t>
+          <t>stimuli/flower/flower_15.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3113,7 +3113,7 @@
         <v>17</v>
       </c>
       <c r="V27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W27" t="n">
         <v>15</v>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_28.jpg</t>
+          <t>stimuli/hammer/hammer_43.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3212,7 +3212,7 @@
         <v>15</v>
       </c>
       <c r="V28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
         <v>16</v>
@@ -3242,12 +3242,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_16.jpg</t>
+          <t>stimuli/jacket/jacket_14.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3308,10 +3308,10 @@
         <v>15</v>
       </c>
       <c r="U29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V29" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W29" t="n">
         <v>14</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_16.jpg</t>
+          <t>stimuli/jacket/jacket_14.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3346,17 +3346,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_06.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_06.jpg</t>
+          <t>stimuli/house/house_34.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3404,16 +3404,16 @@
         <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U30" t="n">
         <v>3</v>
       </c>
       <c r="V30" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W30" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -3440,12 +3440,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_49.jpg</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_14.jpg</t>
+          <t>stimuli/dog/dog_16.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3460,12 +3460,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3506,10 +3506,10 @@
         <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W31" t="n">
         <v>14</v>
@@ -3534,42 +3534,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_49.jpg</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_06.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_18.jpg</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_22.jpg</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_34.jpg</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>6</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U32" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="V32" t="n">
+        <v>8</v>
+      </c>
+      <c r="W32" t="n">
         <v>4</v>
-      </c>
-      <c r="W32" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="33">
@@ -3633,17 +3633,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_06.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/ball/ball_49.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3653,17 +3653,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3701,13 +3701,13 @@
         <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V33" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W33" t="n">
         <v>14</v>
@@ -3732,12 +3732,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/ball/ball_49.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3800,10 +3800,10 @@
         <v>8</v>
       </c>
       <c r="T34" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U34" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="V34" t="n">
         <v>18</v>
@@ -3831,42 +3831,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/ball/ball_49.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_28.jpg</t>
+          <t>stimuli/hammer/hammer_43.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_16.jpg</t>
+          <t>stimuli/jacket/jacket_14.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_06.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3899,16 +3899,16 @@
         <v>9</v>
       </c>
       <c r="T35" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W35" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -3930,42 +3930,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_43.jpg</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_16.jpg</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_22.jpg</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_14.jpg</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_34.jpg</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_49.jpg</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>ball</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3998,16 +3998,16 @@
         <v>10</v>
       </c>
       <c r="T36" t="n">
+        <v>7</v>
+      </c>
+      <c r="U36" t="n">
+        <v>5</v>
+      </c>
+      <c r="V36" t="n">
+        <v>4</v>
+      </c>
+      <c r="W36" t="n">
         <v>6</v>
-      </c>
-      <c r="U36" t="n">
-        <v>10</v>
-      </c>
-      <c r="V36" t="n">
-        <v>9</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_14.jpg</t>
+          <t>stimuli/dog/dog_16.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/house/house_34.jpg</t>
+          <t>stimuli/chair/chair_22.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4044,17 +4044,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4097,16 +4097,16 @@
         <v>11</v>
       </c>
       <c r="T37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U37" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="V37" t="n">
         <v>15</v>
       </c>
       <c r="W37" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
@@ -4128,14 +4128,14 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_22.jpg</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>stimuli/house/house_34.jpg</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_06.jpg</t>
-        </is>
-      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>stimuli/glasses/glasses_36.jpg</t>
@@ -4143,19 +4143,19 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_16.jpg</t>
+          <t>stimuli/jacket/jacket_14.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>glasses</t>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4196,16 +4196,16 @@
         <v>12</v>
       </c>
       <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
         <v>9</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2</v>
       </c>
       <c r="V38" t="n">
         <v>18</v>
       </c>
       <c r="W38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_06.jpg</t>
+          <t>stimuli/house/house_34.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4237,17 +4237,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_16.jpg</t>
+          <t>stimuli/jacket/jacket_14.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_28.jpg</t>
+          <t>stimuli/hammer/hammer_43.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4257,12 +4257,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4295,16 +4295,16 @@
         <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U39" t="n">
         <v>14</v>
       </c>
       <c r="V39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_21.jpg</t>
+          <t>stimuli/bicycle/bicycle_23.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4499,7 +4499,7 @@
         <v>16</v>
       </c>
       <c r="V41" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W41" t="n">
         <v>17</v>
@@ -4529,17 +4529,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/house/house_41.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_44.jpg</t>
+          <t>stimuli/flower/flower_15.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_20.jpg</t>
+          <t>stimuli/dog/dog_10.jpg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4549,17 +4549,17 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4595,13 +4595,13 @@
         <v>16</v>
       </c>
       <c r="U42" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="V42" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -4623,17 +4623,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>stimuli/house/house_41.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/hand/hand_23.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_23.jpg</t>
+          <t>stimuli/ball/ball_44.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4643,17 +4643,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4691,13 +4691,13 @@
         <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="U43" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V43" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W43" t="n">
         <v>13</v>
@@ -4722,12 +4722,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/hand/hand_23.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_44.jpg</t>
+          <t>stimuli/flower/flower_15.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4790,10 +4790,10 @@
         <v>5</v>
       </c>
       <c r="T44" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V44" t="n">
         <v>3</v>
@@ -4821,42 +4821,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_44.jpg</t>
+          <t>stimuli/flower/flower_15.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_20.jpg</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_41.jpg</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_10.jpg</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_23.jpg</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_20.jpg</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4889,16 +4889,16 @@
         <v>6</v>
       </c>
       <c r="T45" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U45" t="n">
+        <v>10</v>
+      </c>
+      <c r="V45" t="n">
+        <v>9</v>
+      </c>
+      <c r="W45" t="n">
         <v>5</v>
-      </c>
-      <c r="V45" t="n">
-        <v>2</v>
-      </c>
-      <c r="W45" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="46">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/jacket/jacket_20.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_15.jpg</t>
+          <t>stimuli/hammer/hammer_21.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4935,17 +4935,17 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>stimuli/house/house_41.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4988,16 +4988,16 @@
         <v>7</v>
       </c>
       <c r="T46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V46" t="n">
         <v>15</v>
       </c>
       <c r="W46" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_15.jpg</t>
+          <t>stimuli/hammer/hammer_21.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_23.jpg</t>
+          <t>stimuli/house/house_41.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5034,17 +5034,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/hand/hand_23.jpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5087,16 +5087,16 @@
         <v>8</v>
       </c>
       <c r="T47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U47" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V47" t="n">
         <v>16</v>
       </c>
       <c r="W47" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
@@ -5118,42 +5118,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>stimuli/house/house_41.jpg</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_44.jpg</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_23.jpg</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_23.jpg</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_21.jpg</t>
-        </is>
-      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/jacket/jacket_20.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5186,16 +5186,16 @@
         <v>9</v>
       </c>
       <c r="T48" t="n">
+        <v>9</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="n">
         <v>2</v>
       </c>
-      <c r="U48" t="n">
-        <v>8</v>
-      </c>
-      <c r="V48" t="n">
-        <v>7</v>
-      </c>
       <c r="W48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49">
@@ -5217,42 +5217,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_23.jpg</t>
+          <t>stimuli/ball/ball_44.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_23.jpg</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_29.jpg</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_21.jpg</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>stimuli/phone/phone_29.jpg</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_15.jpg</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t>hammer</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5285,16 +5285,16 @@
         <v>10</v>
       </c>
       <c r="T49" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="V49" t="n">
         <v>17</v>
       </c>
       <c r="W49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_21.jpg</t>
+          <t>stimuli/bicycle/bicycle_23.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_20.jpg</t>
+          <t>stimuli/dog/dog_10.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5384,13 +5384,13 @@
         <v>11</v>
       </c>
       <c r="T50" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U50" t="n">
         <v>3</v>
       </c>
       <c r="V50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W50" t="n">
         <v>17</v>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_20.jpg</t>
+          <t>stimuli/dog/dog_10.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_23.jpg</t>
+          <t>stimuli/house/house_41.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5486,13 +5486,13 @@
         <v>3</v>
       </c>
       <c r="U51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V51" t="n">
         <v>17</v>
       </c>
       <c r="W51" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_20.jpg</t>
+          <t>stimuli/dog/dog_10.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_15.jpg</t>
+          <t>stimuli/hammer/hammer_21.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5582,7 +5582,7 @@
         <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U52" t="n">
         <v>13</v>
@@ -5591,7 +5591,7 @@
         <v>15</v>
       </c>
       <c r="W52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_21.jpg</t>
+          <t>stimuli/bicycle/bicycle_23.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5690,7 +5690,7 @@
         <v>16</v>
       </c>
       <c r="W53" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/house/house_34.jpg</t>
+          <t>stimuli/chair/chair_22.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5786,7 +5786,7 @@
         <v>15</v>
       </c>
       <c r="V54" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="W54" t="n">
         <v>16</v>
@@ -5816,12 +5816,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_16.jpg</t>
+          <t>stimuli/jacket/jacket_14.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_49.jpg</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5836,12 +5836,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5882,10 +5882,10 @@
         <v>15</v>
       </c>
       <c r="U55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V55" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W55" t="n">
         <v>14</v>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_16.jpg</t>
+          <t>stimuli/jacket/jacket_14.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_28.jpg</t>
+          <t>stimuli/hammer/hammer_43.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5978,13 +5978,13 @@
         <v>4</v>
       </c>
       <c r="T56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U56" t="n">
         <v>3</v>
       </c>
       <c r="V56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W56" t="n">
         <v>16</v>
@@ -6014,17 +6014,17 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_49.jpg</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_14.jpg</t>
+          <t>stimuli/dog/dog_16.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_06.jpg</t>
+          <t>stimuli/house/house_34.jpg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6034,17 +6034,17 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6080,13 +6080,13 @@
         <v>3</v>
       </c>
       <c r="U57" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W57" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
@@ -6108,19 +6108,19 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_28.jpg</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_06.jpg</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_49.jpg</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_43.jpg</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_18.jpg</t>
-        </is>
-      </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>stimuli/lamp/lamp_40.jpg</t>
@@ -6128,17 +6128,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t>ball</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>hand</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6176,13 +6176,13 @@
         <v>6</v>
       </c>
       <c r="T58" t="n">
+        <v>6</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
+      </c>
+      <c r="V58" t="n">
         <v>1</v>
-      </c>
-      <c r="U58" t="n">
-        <v>7</v>
-      </c>
-      <c r="V58" t="n">
-        <v>8</v>
       </c>
       <c r="W58" t="n">
         <v>14</v>
@@ -6207,17 +6207,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_06.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_06.jpg</t>
+          <t>stimuli/house/house_34.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6227,17 +6227,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6275,13 +6275,13 @@
         <v>7</v>
       </c>
       <c r="T59" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U59" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V59" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W59" t="n">
         <v>18</v>
@@ -6306,12 +6306,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/ball/ball_49.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6374,10 +6374,10 @@
         <v>8</v>
       </c>
       <c r="T60" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U60" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="V60" t="n">
         <v>14</v>
@@ -6405,12 +6405,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/ball/ball_49.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_28.jpg</t>
+          <t>stimuli/hammer/hammer_43.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -6425,12 +6425,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6473,10 +6473,10 @@
         <v>9</v>
       </c>
       <c r="T61" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V61" t="n">
         <v>16</v>
@@ -6504,12 +6504,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_28.jpg</t>
+          <t>stimuli/hammer/hammer_43.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_14.jpg</t>
+          <t>stimuli/dog/dog_16.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_06.jpg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6572,16 +6572,16 @@
         <v>10</v>
       </c>
       <c r="T62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V62" t="n">
         <v>3</v>
       </c>
       <c r="W62" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -6603,42 +6603,42 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_16.jpg</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_22.jpg</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_14.jpg</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_34.jpg</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_16.jpg</t>
-        </is>
-      </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_49.jpg</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6671,16 +6671,16 @@
         <v>11</v>
       </c>
       <c r="T63" t="n">
+        <v>5</v>
+      </c>
+      <c r="U63" t="n">
+        <v>4</v>
+      </c>
+      <c r="V63" t="n">
         <v>10</v>
       </c>
-      <c r="U63" t="n">
-        <v>9</v>
-      </c>
-      <c r="V63" t="n">
-        <v>5</v>
-      </c>
       <c r="W63" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
@@ -6702,42 +6702,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_22.jpg</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>stimuli/house/house_34.jpg</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_06.jpg</t>
-        </is>
-      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_28.jpg</t>
+          <t>stimuli/hammer/hammer_43.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6770,16 +6770,16 @@
         <v>12</v>
       </c>
       <c r="T64" t="n">
+        <v>4</v>
+      </c>
+      <c r="U64" t="n">
         <v>9</v>
       </c>
-      <c r="U64" t="n">
-        <v>2</v>
-      </c>
       <c r="V64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -6801,42 +6801,42 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
+          <t>stimuli/house/house_34.jpg</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_40.jpg</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>stimuli/glasses/glasses_36.jpg</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_06.jpg</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>stimuli/lamp/lamp_40.jpg</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>stimuli/glasses/glasses_36.jpg</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_43.jpg</t>
-        </is>
-      </c>
       <c r="I65" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>glasses</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hammer</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6869,7 +6869,7 @@
         <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U65" t="n">
         <v>14</v>
@@ -6878,7 +6878,7 @@
         <v>18</v>
       </c>
       <c r="W65" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_28.jpg</t>
+          <t>stimuli/hammer/hammer_43.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6977,7 +6977,7 @@
         <v>15</v>
       </c>
       <c r="W66" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_20.jpg</t>
+          <t>stimuli/dog/dog_10.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7073,7 +7073,7 @@
         <v>16</v>
       </c>
       <c r="V67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W67" t="n">
         <v>17</v>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>stimuli/house/house_41.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_23.jpg</t>
+          <t>stimuli/ball/ball_44.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7169,10 +7169,10 @@
         <v>16</v>
       </c>
       <c r="U68" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="V68" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W68" t="n">
         <v>13</v>
@@ -7197,17 +7197,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>stimuli/house/house_41.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/hand/hand_23.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_44.jpg</t>
+          <t>stimuli/flower/flower_15.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7217,17 +7217,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7265,13 +7265,13 @@
         <v>4</v>
       </c>
       <c r="T69" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="U69" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V69" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W69" t="n">
         <v>17</v>
@@ -7296,12 +7296,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/hand/hand_23.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_44.jpg</t>
+          <t>stimuli/flower/flower_15.jpg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -7316,12 +7316,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -7364,10 +7364,10 @@
         <v>5</v>
       </c>
       <c r="T70" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U70" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V70" t="n">
         <v>3</v>
@@ -7395,17 +7395,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_44.jpg</t>
+          <t>stimuli/flower/flower_15.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/jacket/jacket_20.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_21.jpg</t>
+          <t>stimuli/bicycle/bicycle_23.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7415,17 +7415,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7463,13 +7463,13 @@
         <v>6</v>
       </c>
       <c r="T71" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V71" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W71" t="n">
         <v>17</v>
@@ -7494,17 +7494,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/jacket/jacket_20.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_15.jpg</t>
+          <t>stimuli/hammer/hammer_21.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_23.jpg</t>
+          <t>stimuli/house/house_41.jpg</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7514,17 +7514,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7562,13 +7562,13 @@
         <v>7</v>
       </c>
       <c r="T72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U72" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V72" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W72" t="n">
         <v>3</v>
@@ -7593,17 +7593,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_15.jpg</t>
+          <t>stimuli/hammer/hammer_21.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_23.jpg</t>
+          <t>stimuli/house/house_41.jpg</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_23.jpg</t>
+          <t>stimuli/ball/ball_44.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7613,17 +7613,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7661,13 +7661,13 @@
         <v>8</v>
       </c>
       <c r="T73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U73" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V73" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W73" t="n">
         <v>16</v>
@@ -7692,12 +7692,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_23.jpg</t>
+          <t>stimuli/house/house_41.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_23.jpg</t>
+          <t>stimuli/ball/ball_44.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7760,10 +7760,10 @@
         <v>9</v>
       </c>
       <c r="T74" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U74" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="V74" t="n">
         <v>13</v>
@@ -7791,42 +7791,42 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_44.jpg</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_23.jpg</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_10.jpg</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_23.jpg</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_21.jpg</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_20.jpg</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_10.jpg</t>
-        </is>
-      </c>
       <c r="I75" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
           <t>hand</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7859,16 +7859,16 @@
         <v>10</v>
       </c>
       <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
+      </c>
+      <c r="V75" t="n">
+        <v>5</v>
+      </c>
+      <c r="W75" t="n">
         <v>8</v>
-      </c>
-      <c r="U75" t="n">
-        <v>7</v>
-      </c>
-      <c r="V75" t="n">
-        <v>10</v>
-      </c>
-      <c r="W75" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="76">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_21.jpg</t>
+          <t>stimuli/bicycle/bicycle_23.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/jacket/jacket_20.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7958,7 +7958,7 @@
         <v>11</v>
       </c>
       <c r="T76" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U76" t="n">
         <v>3</v>
@@ -7967,7 +7967,7 @@
         <v>15</v>
       </c>
       <c r="W76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77">
@@ -7994,17 +7994,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_20.jpg</t>
+          <t>stimuli/dog/dog_10.jpg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>stimuli/house/house_41.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_15.jpg</t>
+          <t>stimuli/hammer/hammer_21.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8014,17 +8014,17 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8060,13 +8060,13 @@
         <v>3</v>
       </c>
       <c r="U77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V77" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="W77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_20.jpg</t>
+          <t>stimuli/dog/dog_10.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_23.jpg</t>
+          <t>stimuli/ball/ball_44.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8156,7 +8156,7 @@
         <v>13</v>
       </c>
       <c r="T78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U78" t="n">
         <v>13</v>
@@ -8165,7 +8165,7 @@
         <v>16</v>
       </c>
       <c r="W78" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_23.jpg</t>
+          <t>stimuli/house/house_41.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8261,7 +8261,7 @@
         <v>17</v>
       </c>
       <c r="V79" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W79" t="n">
         <v>15</v>
@@ -8390,12 +8390,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_16.jpg</t>
+          <t>stimuli/jacket/jacket_14.jpg</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_06.jpg</t>
+          <t>stimuli/house/house_34.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8410,12 +8410,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8456,10 +8456,10 @@
         <v>15</v>
       </c>
       <c r="U81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V81" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W81" t="n">
         <v>16</v>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_16.jpg</t>
+          <t>stimuli/jacket/jacket_14.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/house/house_34.jpg</t>
+          <t>stimuli/chair/chair_22.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8552,13 +8552,13 @@
         <v>4</v>
       </c>
       <c r="T82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U82" t="n">
         <v>3</v>
       </c>
       <c r="V82" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="W82" t="n">
         <v>14</v>
@@ -8588,17 +8588,17 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_28.jpg</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_49.jpg</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_18.jpg</t>
-        </is>
-      </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_06.jpg</t>
+          <t>stimuli/house/house_34.jpg</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8608,17 +8608,17 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8654,13 +8654,13 @@
         <v>3</v>
       </c>
       <c r="U83" t="n">
+        <v>6</v>
+      </c>
+      <c r="V83" t="n">
         <v>1</v>
       </c>
-      <c r="V83" t="n">
-        <v>8</v>
-      </c>
       <c r="W83" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_49.jpg</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_06.jpg</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -8697,17 +8697,17 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_16.jpg</t>
+          <t>stimuli/jacket/jacket_14.jpg</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8750,16 +8750,16 @@
         <v>6</v>
       </c>
       <c r="T84" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U84" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="V84" t="n">
         <v>18</v>
       </c>
       <c r="W84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85">
@@ -8781,17 +8781,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_06.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_14.jpg</t>
+          <t>stimuli/dog/dog_16.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8801,17 +8801,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8849,13 +8849,13 @@
         <v>7</v>
       </c>
       <c r="T85" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U85" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W85" t="n">
         <v>14</v>
@@ -8880,17 +8880,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/ball/ball_49.jpg</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_28.jpg</t>
+          <t>stimuli/hammer/hammer_43.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8900,17 +8900,17 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8948,13 +8948,13 @@
         <v>8</v>
       </c>
       <c r="T86" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U86" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="V86" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W86" t="n">
         <v>16</v>
@@ -8979,12 +8979,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/ball/ball_49.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_28.jpg</t>
+          <t>stimuli/hammer/hammer_43.jpg</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -8999,12 +8999,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -9047,10 +9047,10 @@
         <v>9</v>
       </c>
       <c r="T87" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U87" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V87" t="n">
         <v>15</v>
@@ -9078,42 +9078,42 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_43.jpg</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_16.jpg</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_14.jpg</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_49.jpg</t>
-        </is>
-      </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9146,16 +9146,16 @@
         <v>10</v>
       </c>
       <c r="T88" t="n">
+        <v>7</v>
+      </c>
+      <c r="U88" t="n">
+        <v>5</v>
+      </c>
+      <c r="V88" t="n">
         <v>6</v>
       </c>
-      <c r="U88" t="n">
-        <v>10</v>
-      </c>
-      <c r="V88" t="n">
-        <v>1</v>
-      </c>
       <c r="W88" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89">
@@ -9177,42 +9177,42 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_16.jpg</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_22.jpg</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_14.jpg</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_34.jpg</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_16.jpg</t>
-        </is>
-      </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_06.jpg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -9245,16 +9245,16 @@
         <v>11</v>
       </c>
       <c r="T89" t="n">
+        <v>5</v>
+      </c>
+      <c r="U89" t="n">
+        <v>4</v>
+      </c>
+      <c r="V89" t="n">
         <v>10</v>
       </c>
-      <c r="U89" t="n">
-        <v>9</v>
-      </c>
-      <c r="V89" t="n">
-        <v>5</v>
-      </c>
       <c r="W89" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -9276,14 +9276,14 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_22.jpg</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t>stimuli/house/house_34.jpg</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_06.jpg</t>
-        </is>
-      </c>
       <c r="G90" t="inlineStr">
         <is>
           <t>stimuli/glasses/glasses_36.jpg</t>
@@ -9291,19 +9291,19 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_22.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
       <c r="K90" t="inlineStr">
         <is>
           <t>glasses</t>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -9344,16 +9344,16 @@
         <v>12</v>
       </c>
       <c r="T90" t="n">
+        <v>4</v>
+      </c>
+      <c r="U90" t="n">
         <v>9</v>
-      </c>
-      <c r="U90" t="n">
-        <v>2</v>
       </c>
       <c r="V90" t="n">
         <v>18</v>
       </c>
       <c r="W90" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91">
@@ -9375,42 +9375,42 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
+          <t>stimuli/house/house_34.jpg</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_40.jpg</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>stimuli/key/key_26.jpg</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_06.jpg</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>stimuli/lamp/lamp_40.jpg</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>stimuli/key/key_26.jpg</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_43.jpg</t>
-        </is>
-      </c>
       <c r="I91" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>hammer</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -9443,7 +9443,7 @@
         <v>13</v>
       </c>
       <c r="T91" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U91" t="n">
         <v>14</v>
@@ -9452,7 +9452,7 @@
         <v>15</v>
       </c>
       <c r="W91" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -9484,12 +9484,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_16.jpg</t>
+          <t>stimuli/jacket/jacket_14.jpg</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/ball/ball_49.jpg</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -9548,10 +9548,10 @@
         <v>16</v>
       </c>
       <c r="V92" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W92" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/hand/hand_23.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9647,7 +9647,7 @@
         <v>16</v>
       </c>
       <c r="V93" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W93" t="n">
         <v>17</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>stimuli/house/house_41.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_21.jpg</t>
+          <t>stimuli/bicycle/bicycle_23.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9697,12 +9697,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9743,10 +9743,10 @@
         <v>16</v>
       </c>
       <c r="U94" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="V94" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W94" t="n">
         <v>13</v>
@@ -9771,17 +9771,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>stimuli/house/house_41.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/hand/hand_23.jpg</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_20.jpg</t>
+          <t>stimuli/dog/dog_10.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -9791,17 +9791,17 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9839,13 +9839,13 @@
         <v>4</v>
       </c>
       <c r="T95" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="U95" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W95" t="n">
         <v>17</v>
@@ -9870,17 +9870,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/hand/hand_23.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_44.jpg</t>
+          <t>stimuli/flower/flower_15.jpg</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_23.jpg</t>
+          <t>stimuli/house/house_41.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9890,17 +9890,17 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9938,13 +9938,13 @@
         <v>5</v>
       </c>
       <c r="T96" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U96" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V96" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W96" t="n">
         <v>13</v>
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_44.jpg</t>
+          <t>stimuli/flower/flower_15.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/jacket/jacket_20.jpg</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -9989,12 +9989,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -10037,10 +10037,10 @@
         <v>6</v>
       </c>
       <c r="T97" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V97" t="n">
         <v>3</v>
@@ -10068,42 +10068,42 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_20.jpg</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_21.jpg</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_44.jpg</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_10.jpg</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_15.jpg</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_23.jpg</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_20.jpg</t>
-        </is>
-      </c>
       <c r="I98" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -10136,16 +10136,16 @@
         <v>7</v>
       </c>
       <c r="T98" t="n">
+        <v>10</v>
+      </c>
+      <c r="U98" t="n">
+        <v>7</v>
+      </c>
+      <c r="V98" t="n">
+        <v>1</v>
+      </c>
+      <c r="W98" t="n">
         <v>5</v>
-      </c>
-      <c r="U98" t="n">
-        <v>6</v>
-      </c>
-      <c r="V98" t="n">
-        <v>8</v>
-      </c>
-      <c r="W98" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="99">
@@ -10167,42 +10167,42 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_21.jpg</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_41.jpg</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_10.jpg</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_15.jpg</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_23.jpg</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_20.jpg</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_44.jpg</t>
-        </is>
-      </c>
       <c r="I99" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>ball</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -10235,16 +10235,16 @@
         <v>8</v>
       </c>
       <c r="T99" t="n">
+        <v>7</v>
+      </c>
+      <c r="U99" t="n">
+        <v>9</v>
+      </c>
+      <c r="V99" t="n">
+        <v>5</v>
+      </c>
+      <c r="W99" t="n">
         <v>6</v>
-      </c>
-      <c r="U99" t="n">
-        <v>2</v>
-      </c>
-      <c r="V99" t="n">
-        <v>10</v>
-      </c>
-      <c r="W99" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -10266,19 +10266,19 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
+          <t>stimuli/house/house_41.jpg</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_44.jpg</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_23.jpg</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_23.jpg</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_21.jpg</t>
-        </is>
-      </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>stimuli/key/key_17.jpg</t>
@@ -10286,17 +10286,17 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>hammer</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -10334,13 +10334,13 @@
         <v>9</v>
       </c>
       <c r="T100" t="n">
+        <v>9</v>
+      </c>
+      <c r="U100" t="n">
+        <v>1</v>
+      </c>
+      <c r="V100" t="n">
         <v>2</v>
-      </c>
-      <c r="U100" t="n">
-        <v>8</v>
-      </c>
-      <c r="V100" t="n">
-        <v>7</v>
       </c>
       <c r="W100" t="n">
         <v>15</v>
@@ -10365,42 +10365,42 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_23.jpg</t>
+          <t>stimuli/ball/ball_44.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_23.jpg</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_15.jpg</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_21.jpg</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_44.jpg</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_15.jpg</t>
-        </is>
-      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
           <t>hammer</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -10433,16 +10433,16 @@
         <v>10</v>
       </c>
       <c r="T101" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U101" t="n">
+        <v>2</v>
+      </c>
+      <c r="V101" t="n">
+        <v>6</v>
+      </c>
+      <c r="W101" t="n">
         <v>7</v>
-      </c>
-      <c r="V101" t="n">
-        <v>1</v>
-      </c>
-      <c r="W101" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="102">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_21.jpg</t>
+          <t>stimuli/bicycle/bicycle_23.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -10479,12 +10479,12 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/jacket/jacket_20.jpg</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -10532,7 +10532,7 @@
         <v>11</v>
       </c>
       <c r="T102" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U102" t="n">
         <v>3</v>
@@ -10541,7 +10541,7 @@
         <v>13</v>
       </c>
       <c r="W102" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_20.jpg</t>
+          <t>stimuli/dog/dog_10.jpg</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_23.jpg</t>
+          <t>stimuli/house/house_41.jpg</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -10634,13 +10634,13 @@
         <v>3</v>
       </c>
       <c r="U103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V103" t="n">
         <v>16</v>
       </c>
       <c r="W103" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="104">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_20.jpg</t>
+          <t>stimuli/dog/dog_10.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>stimuli/house/house_41.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10730,7 +10730,7 @@
         <v>13</v>
       </c>
       <c r="T104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U104" t="n">
         <v>13</v>
@@ -10739,7 +10739,7 @@
         <v>15</v>
       </c>
       <c r="W104" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
